--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91896</v>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92507</v>
+        <v>92510</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91905</v>
+        <v>91906</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92510</v>
+        <v>92511</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91906</v>
+        <v>91911</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136607418</v>
       </c>
       <c r="B3" t="n">
-        <v>85694</v>
+        <v>85696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92511</v>
+        <v>92516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136607428</v>
       </c>
       <c r="B5" t="n">
-        <v>83444</v>
+        <v>83446</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136607528</v>
       </c>
       <c r="B6" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136607740</v>
       </c>
       <c r="B7" t="n">
-        <v>58165</v>
+        <v>58167</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91911</v>
+        <v>91913</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136607418</v>
       </c>
       <c r="B3" t="n">
-        <v>85696</v>
+        <v>85697</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92516</v>
+        <v>92518</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91913</v>
+        <v>91915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136607418</v>
       </c>
       <c r="B3" t="n">
-        <v>85697</v>
+        <v>85701</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92518</v>
+        <v>92520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136607428</v>
       </c>
       <c r="B5" t="n">
-        <v>83446</v>
+        <v>83450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91915</v>
+        <v>91917</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136607418</v>
       </c>
       <c r="B3" t="n">
-        <v>85701</v>
+        <v>85703</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136607428</v>
       </c>
       <c r="B5" t="n">
-        <v>83450</v>
+        <v>83452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91917</v>
+        <v>91918</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136607418</v>
       </c>
       <c r="B3" t="n">
-        <v>85703</v>
+        <v>85704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92522</v>
+        <v>92523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136607428</v>
       </c>
       <c r="B5" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91918</v>
+        <v>91924</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136607418</v>
       </c>
       <c r="B3" t="n">
-        <v>85704</v>
+        <v>85706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92523</v>
+        <v>92529</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91924</v>
+        <v>91928</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136607418</v>
       </c>
       <c r="B3" t="n">
-        <v>85706</v>
+        <v>85710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92529</v>
+        <v>92533</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136607428</v>
       </c>
       <c r="B5" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91928</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136607418</v>
       </c>
       <c r="B3" t="n">
-        <v>85710</v>
+        <v>85712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92533</v>
+        <v>92535</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136607428</v>
       </c>
       <c r="B5" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136607431</v>
       </c>
       <c r="B2" t="n">
-        <v>91930</v>
+        <v>91943</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136607418</v>
       </c>
       <c r="B3" t="n">
-        <v>85712</v>
+        <v>85725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136607440</v>
       </c>
       <c r="B4" t="n">
-        <v>92535</v>
+        <v>92548</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136607428</v>
       </c>
       <c r="B5" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136607528</v>
       </c>
       <c r="B6" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
         <v>136607740</v>
       </c>
       <c r="B7" t="n">
-        <v>58167</v>
+        <v>58180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -790,51 +790,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136607418</v>
+        <v>137390303</v>
       </c>
       <c r="B3" t="n">
-        <v>85725</v>
+        <v>91969</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1971</v>
+        <v>1067</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stor sotdyna</t>
+          <t>Vedlavklubba</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Camarops polysperma</t>
+          <t>Multiclavula mucida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Mont.) J.H.Mill.</t>
+          <t>(Pers.) R.H.Petersen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>död grov bokstam av evighetskaraktär, Linneröd, Sk</t>
+          <t>Lycke, Sk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392505</v>
+        <v>392517</v>
       </c>
       <c r="R3" t="n">
-        <v>6223761</v>
+        <v>6223769</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,12 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,38 +879,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136607418</t>
+          <t>https://artportalen.se/Sighting/137390303</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136607440</v>
+        <v>136607418</v>
       </c>
       <c r="B4" t="n">
-        <v>92548</v>
+        <v>85725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2023</v>
+        <v>1971</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sydlig sotticka</t>
+          <t>Stor sotdyna</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ischnoderma resinosum</t>
+          <t>Camarops polysperma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schrad.) P.Karst.</t>
+          <t>(Mont.) J.H.Mill.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -1004,38 +1006,38 @@
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136607440</t>
+          <t>https://artportalen.se/Sighting/136607418</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136607428</v>
+        <v>136607440</v>
       </c>
       <c r="B5" t="n">
-        <v>83472</v>
+        <v>92548</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6439</v>
+        <v>2023</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulnål</t>
+          <t>Sydlig sotticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca brachypoda</t>
+          <t>Ischnoderma resinosum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Tibell</t>
+          <t>(Schrad.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1114,66 +1116,57 @@
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136607428</t>
+          <t>https://artportalen.se/Sighting/136607440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136607528</v>
+        <v>136607428</v>
       </c>
       <c r="B6" t="n">
-        <v>58180</v>
+        <v>83472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>6439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Gulnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Chaenotheca brachypoda</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Tibell</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bokskog med föryngring av gran och bok, Linneröd, Sk</t>
+          <t>död grov bokstam av evighetskaraktär, Linneröd, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>392975</v>
+        <v>392505</v>
       </c>
       <c r="R6" t="n">
-        <v>6223781</v>
+        <v>6223761</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1211,6 +1204,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,13 +1226,13 @@
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136607528</t>
+          <t>https://artportalen.se/Sighting/136607428</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136607740</v>
+        <v>136607528</v>
       </c>
       <c r="B7" t="n">
         <v>58180</v>
@@ -1268,7 +1262,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1281,17 +1275,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bokskog med tät bokföryngring, Linneröd, Sk</t>
+          <t>Bokskog med föryngring av gran och bok, Linneröd, Sk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>392443</v>
+        <v>392975</v>
       </c>
       <c r="R7" t="n">
-        <v>6223768</v>
+        <v>6223781</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1349,6 +1343,124 @@
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136607528</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>136607740</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58180</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bokskog med tät bokföryngring, Linneröd, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>392443</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6223768</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136607740</t>
         </is>
@@ -1362,6 +1474,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ8"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,7 +793,7 @@
         <v>137390303</v>
       </c>
       <c r="B3" t="n">
-        <v>91969</v>
+        <v>91981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1463,6 +1463,254 @@
       <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136607740</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>137430770</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58194</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lycke ost bäcken, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>392885</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6223757</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137430770</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>137430772</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103041</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bergfink</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fringilla montifringilla</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lycke ost bäcken, Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>392885</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6223757</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vedby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137430772</t>
         </is>
       </c>
     </row>
@@ -1475,6 +1723,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137390303</v>
       </c>
       <c r="B3" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137390303</v>
       </c>
       <c r="B3" t="n">
-        <v>91982</v>
+        <v>91985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37092-2026 artfynd.xlsx
+++ b/artfynd/A 37092-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>137390303</v>
       </c>
       <c r="B3" t="n">
-        <v>91985</v>
+        <v>91989</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1471,7 +1471,7 @@
         <v>137430770</v>
       </c>
       <c r="B9" t="n">
-        <v>58194</v>
+        <v>58197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>137430772</v>
       </c>
       <c r="B10" t="n">
-        <v>58658</v>
+        <v>58661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
